--- a/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-matrices.xlsx
+++ b/docs/attack-excel-files/v18.1/russia-colonialism/russia-colonialism-v18.1-matrices.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="106">
   <si>
     <t>Легитимизация доминирования</t>
   </si>
@@ -1468,7 +1468,7 @@
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>68</v>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E13" s="4"/>
       <c r="F13" s="2" t="s">
@@ -1494,7 +1494,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>48</v>
@@ -1505,7 +1505,7 @@
         <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>69</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="D16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="2" t="s">
@@ -1525,7 +1525,7 @@
     </row>
     <row r="17" spans="4:6">
       <c r="D17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>9</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="18" spans="4:6">
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>33</v>
@@ -1541,7 +1541,7 @@
     </row>
     <row r="19" spans="4:6">
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>70</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="20" spans="4:6">
       <c r="D20" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>71</v>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="21" spans="4:6">
       <c r="D21" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="2" t="s">
@@ -1569,7 +1569,7 @@
     </row>
     <row r="22" spans="4:6">
       <c r="D22" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="2" t="s">
@@ -1578,7 +1578,7 @@
     </row>
     <row r="23" spans="4:6">
       <c r="D23" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>72</v>
@@ -1586,16 +1586,13 @@
     </row>
     <row r="24" spans="4:6">
       <c r="D24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="4:6">
-      <c r="D25" t="s">
-        <v>62</v>
-      </c>
       <c r="E25" s="1" t="s">
         <v>74</v>
       </c>
